--- a/database/event/7437/event_7437_evp_summary.xlsx
+++ b/database/event/7437/event_7437_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.0106</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.769</v>
       </c>
       <c r="D2" t="n">
         <v>2.8147</v>
@@ -545,7 +545,7 @@
         <v>7.3236</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="D3" t="n">
         <v>2.5372</v>
@@ -591,7 +591,7 @@
         <v>6.4535</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.2307</v>
       </c>
       <c r="D4" t="n">
         <v>2.1857</v>
@@ -637,7 +637,7 @@
         <v>5.5045</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.9027</v>
       </c>
       <c r="D5" t="n">
         <v>1.8023</v>
@@ -683,7 +683,7 @@
         <v>5.2583</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.8176</v>
       </c>
       <c r="D6" t="n">
         <v>1.7029</v>
@@ -729,7 +729,7 @@
         <v>5.2066</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="D7" t="n">
         <v>1.682</v>
@@ -775,7 +775,7 @@
         <v>5.0817</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.7566</v>
       </c>
       <c r="D8" t="n">
         <v>1.6315</v>
@@ -821,7 +821,7 @@
         <v>4.826</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.6682</v>
       </c>
       <c r="D9" t="n">
         <v>1.5282</v>
@@ -867,7 +867,7 @@
         <v>3.8929</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.3456</v>
       </c>
       <c r="D10" t="n">
         <v>1.1513</v>
@@ -913,7 +913,7 @@
         <v>3.7755</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.3051</v>
       </c>
       <c r="D11" t="n">
         <v>1.1039</v>
@@ -959,7 +959,7 @@
         <v>3.6479</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.2609</v>
       </c>
       <c r="D12" t="n">
         <v>1.0523</v>
@@ -1005,7 +1005,7 @@
         <v>3.1791</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.0989</v>
       </c>
       <c r="D13" t="n">
         <v>0.8629</v>
@@ -1051,7 +1051,7 @@
         <v>3.0574</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.0568</v>
       </c>
       <c r="D14" t="n">
         <v>0.8138</v>
@@ -1097,7 +1097,7 @@
         <v>2.834</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.9796</v>
       </c>
       <c r="D15" t="n">
         <v>0.7235</v>
@@ -1143,7 +1143,7 @@
         <v>2.631</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.9094</v>
       </c>
       <c r="D16" t="n">
         <v>0.6415</v>
@@ -1189,7 +1189,7 @@
         <v>2.316</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.8006</v>
       </c>
       <c r="D17" t="n">
         <v>0.5143</v>
@@ -1235,7 +1235,7 @@
         <v>2.077</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.7179</v>
       </c>
       <c r="D18" t="n">
         <v>0.4177</v>
@@ -1281,7 +1281,7 @@
         <v>2.0558</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.7106</v>
       </c>
       <c r="D19" t="n">
         <v>0.4091</v>
@@ -1327,7 +1327,7 @@
         <v>2.0506</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.7088</v>
       </c>
       <c r="D20" t="n">
         <v>0.407</v>
@@ -1373,7 +1373,7 @@
         <v>1.9937</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.6891</v>
       </c>
       <c r="D21" t="n">
         <v>0.384</v>
@@ -1419,7 +1419,7 @@
         <v>1.964</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="D22" t="n">
         <v>0.3721</v>
@@ -1465,7 +1465,7 @@
         <v>1.7502</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="D23" t="n">
         <v>0.2857</v>
@@ -1511,7 +1511,7 @@
         <v>1.7441</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.6029</v>
       </c>
       <c r="D24" t="n">
         <v>0.2832</v>
@@ -1557,7 +1557,7 @@
         <v>1.6694</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="D25" t="n">
         <v>0.253</v>
@@ -1603,7 +1603,7 @@
         <v>1.6624</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.5746</v>
       </c>
       <c r="D26" t="n">
         <v>0.2502</v>
@@ -1649,7 +1649,7 @@
         <v>1.5735</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="D27" t="n">
         <v>0.2143</v>
@@ -1695,7 +1695,7 @@
         <v>1.5587</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="D28" t="n">
         <v>0.2083</v>
@@ -1741,7 +1741,7 @@
         <v>1.5485</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.5353</v>
       </c>
       <c r="D29" t="n">
         <v>0.2042</v>
@@ -1787,7 +1787,7 @@
         <v>1.5293</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.5286</v>
       </c>
       <c r="D30" t="n">
         <v>0.1964</v>
@@ -1833,7 +1833,7 @@
         <v>1.4455</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.4997</v>
       </c>
       <c r="D31" t="n">
         <v>0.1626</v>
@@ -1879,7 +1879,7 @@
         <v>1.3708</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.4738</v>
       </c>
       <c r="D32" t="n">
         <v>0.1324</v>
@@ -1925,7 +1925,7 @@
         <v>1.2811</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.4428</v>
       </c>
       <c r="D33" t="n">
         <v>0.09619999999999999</v>
@@ -1971,7 +1971,7 @@
         <v>1.2781</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.4418</v>
       </c>
       <c r="D34" t="n">
         <v>0.095</v>
@@ -2017,7 +2017,7 @@
         <v>1.0744</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.3714</v>
       </c>
       <c r="D35" t="n">
         <v>0.0127</v>
@@ -2063,7 +2063,7 @@
         <v>0.9893</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0217</v>
@@ -2109,7 +2109,7 @@
         <v>0.9101</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.3146</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0537</v>
@@ -2155,7 +2155,7 @@
         <v>0.8784</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.3036</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0665</v>
@@ -2201,7 +2201,7 @@
         <v>0.8353</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2887</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0839</v>
@@ -2247,7 +2247,7 @@
         <v>0.6866</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2373</v>
       </c>
       <c r="D40" t="n">
         <v>-0.144</v>
@@ -2293,7 +2293,7 @@
         <v>0.518</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1791</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2121</v>
@@ -2339,7 +2339,7 @@
         <v>0.5155999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.1782</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2131</v>
@@ -2385,7 +2385,7 @@
         <v>0.4559</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1576</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2372</v>
@@ -2431,7 +2431,7 @@
         <v>0.3959</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1368</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2614</v>
@@ -2477,7 +2477,7 @@
         <v>0.3669</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1268</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2731</v>
@@ -2523,7 +2523,7 @@
         <v>0.3618</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1251</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2752</v>
@@ -2569,7 +2569,7 @@
         <v>0.2154</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3343</v>
@@ -2615,7 +2615,7 @@
         <v>0.0989</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0342</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3814</v>
@@ -2661,7 +2661,7 @@
         <v>0.0847</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0293</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3871</v>
@@ -2707,7 +2707,7 @@
         <v>-0.0669</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0231</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4484</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0925</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.032</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4587</v>
@@ -2799,7 +2799,7 @@
         <v>-0.1781</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0616</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4933</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1988</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0687</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5017</v>
@@ -2891,7 +2891,7 @@
         <v>-0.1988</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.0687</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5017</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2067</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5049</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2636</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0911</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5279</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3301</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1141</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5547</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3334</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.1152</v>
       </c>
       <c r="D58" t="n">
         <v>-0.556</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5447</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1883</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6414</v>
@@ -3167,7 +3167,7 @@
         <v>-0.7323</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2531</v>
       </c>
       <c r="D60" t="n">
         <v>-0.7171999999999999</v>
@@ -3213,7 +3213,7 @@
         <v>-0.7983</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2759</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7439</v>
@@ -3259,7 +3259,7 @@
         <v>-0.9025</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.312</v>
       </c>
       <c r="D62" t="n">
         <v>-0.786</v>
@@ -3305,7 +3305,7 @@
         <v>-1.004</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.347</v>
       </c>
       <c r="D63" t="n">
         <v>-0.827</v>
@@ -3351,7 +3351,7 @@
         <v>-1.1109</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.384</v>
       </c>
       <c r="D64" t="n">
         <v>-0.8701</v>
@@ -3397,7 +3397,7 @@
         <v>-1.1836</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4091</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8995</v>
@@ -3443,7 +3443,7 @@
         <v>-1.2076</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4174</v>
       </c>
       <c r="D66" t="n">
         <v>-0.9092</v>
@@ -3489,7 +3489,7 @@
         <v>-1.2396</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.4285</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9221</v>
@@ -3535,7 +3535,7 @@
         <v>-1.2959</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.4479</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9449</v>
@@ -3581,7 +3581,7 @@
         <v>-1.3003</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.4495</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9467</v>
@@ -3627,7 +3627,7 @@
         <v>-1.3153</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.4547</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9527</v>
@@ -3673,7 +3673,7 @@
         <v>-1.445</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.4995</v>
       </c>
       <c r="D71" t="n">
         <v>-1.0051</v>
@@ -3719,7 +3719,7 @@
         <v>-1.451</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.5016</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0075</v>
@@ -3765,7 +3765,7 @@
         <v>-1.4629</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.5057</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0123</v>
@@ -3811,7 +3811,7 @@
         <v>-1.5467</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.5346</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0462</v>
@@ -3857,7 +3857,7 @@
         <v>-1.6202</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0759</v>
@@ -3903,7 +3903,7 @@
         <v>-1.6374</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0828</v>
@@ -3949,7 +3949,7 @@
         <v>-1.9614</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.678</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2137</v>
@@ -3995,7 +3995,7 @@
         <v>-2.0666</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.7143</v>
       </c>
       <c r="D78" t="n">
         <v>-1.2562</v>
@@ -4041,7 +4041,7 @@
         <v>-2.1273</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.7353</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2807</v>
@@ -4087,7 +4087,7 @@
         <v>-4.2088</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.4548</v>
       </c>
       <c r="D80" t="n">
         <v>-2.1216</v>
@@ -4133,7 +4133,7 @@
         <v>-6.3116</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.1817</v>
       </c>
       <c r="D81" t="n">
         <v>-2.9711</v>

--- a/database/event/7437/event_7437_evp_summary.xlsx
+++ b/database/event/7437/event_7437_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.0106</v>
+        <v>7.9799</v>
       </c>
       <c r="C2" t="n">
-        <v>2.769</v>
+        <v>2.7584</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8147</v>
+        <v>2.7353</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0106</v>
+        <v>7.9799</v>
       </c>
       <c r="F2" t="n">
-        <v>4.222</v>
+        <v>4.1913</v>
       </c>
       <c r="G2" t="n">
         <v>3.7886</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3171</v>
+        <v>4.269</v>
       </c>
       <c r="I2" t="n">
         <v>4.3777</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3236</v>
+        <v>7.4288</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5315</v>
+        <v>2.5679</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5372</v>
+        <v>2.5157</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3236</v>
+        <v>7.4288</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6088</v>
+        <v>4.7141</v>
       </c>
       <c r="G3" t="n">
         <v>2.7148</v>
       </c>
       <c r="H3" t="n">
-        <v>5.982</v>
+        <v>6.4054</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8485</v>
+        <v>5.1918</v>
       </c>
       <c r="J3" t="n">
         <v>2.7148</v>
@@ -575,7 +575,7 @@
         <v>106</v>
       </c>
       <c r="M3" t="n">
-        <v>7.5633</v>
+        <v>7.906599999999999</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4535</v>
+        <v>6.7839</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2307</v>
+        <v>2.3449</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1857</v>
+        <v>2.2588</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4535</v>
+        <v>6.7839</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3794</v>
+        <v>1.7098</v>
       </c>
       <c r="G4" t="n">
         <v>5.0741</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3794</v>
+        <v>1.7098</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3923</v>
+        <v>1.7387</v>
       </c>
       <c r="J4" t="n">
         <v>5.0741</v>
@@ -621,7 +621,7 @@
         <v>179</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4664</v>
+        <v>6.812799999999999</v>
       </c>
       <c r="N4" t="n">
         <v>318</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5045</v>
+        <v>6.1417</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9027</v>
+        <v>2.123</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8023</v>
+        <v>2.0029</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5045</v>
+        <v>6.1417</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7903</v>
+        <v>4.4275</v>
       </c>
       <c r="G5" t="n">
         <v>1.7142</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7903</v>
+        <v>4.6392</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8435</v>
+        <v>4.7574</v>
       </c>
       <c r="J5" t="n">
         <v>1.7142</v>
@@ -667,7 +667,7 @@
         <v>106</v>
       </c>
       <c r="M5" t="n">
-        <v>5.557700000000001</v>
+        <v>6.4716</v>
       </c>
       <c r="N5" t="n">
         <v>290</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2583</v>
+        <v>5.3995</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8176</v>
+        <v>1.8664</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7029</v>
+        <v>1.7073</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2583</v>
+        <v>5.3995</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2087</v>
+        <v>3.3499</v>
       </c>
       <c r="G6" t="n">
         <v>2.0496</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2087</v>
+        <v>3.3499</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2386</v>
+        <v>3.4065</v>
       </c>
       <c r="J6" t="n">
         <v>2.0496</v>
@@ -713,7 +713,7 @@
         <v>179</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2882</v>
+        <v>5.456099999999999</v>
       </c>
       <c r="N6" t="n">
         <v>318</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2066</v>
+        <v>5.1901</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7997</v>
+        <v>1.794</v>
       </c>
       <c r="D7" t="n">
-        <v>1.682</v>
+        <v>1.6238</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2066</v>
+        <v>5.1901</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2208</v>
+        <v>2.2043</v>
       </c>
       <c r="G7" t="n">
         <v>2.9858</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2208</v>
+        <v>2.2043</v>
       </c>
       <c r="I7" t="n">
         <v>2.2415</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0817</v>
+        <v>5.0675</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7566</v>
+        <v>1.7516</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6315</v>
+        <v>1.575</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0817</v>
+        <v>5.0675</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9124</v>
+        <v>1.8982</v>
       </c>
       <c r="G8" t="n">
         <v>3.1693</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9124</v>
+        <v>1.8982</v>
       </c>
       <c r="I8" t="n">
         <v>1.9303</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.826</v>
+        <v>4.8883</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6682</v>
+        <v>1.6897</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5282</v>
+        <v>1.5036</v>
       </c>
       <c r="E9" t="n">
-        <v>4.826</v>
+        <v>4.8883</v>
       </c>
       <c r="F9" t="n">
-        <v>4.804</v>
+        <v>4.8663</v>
       </c>
       <c r="G9" t="n">
         <v>0.022</v>
       </c>
       <c r="H9" t="n">
-        <v>6.767</v>
+        <v>7.3321</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4848</v>
+        <v>5.9429</v>
       </c>
       <c r="J9" t="n">
         <v>0.022</v>
@@ -851,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>5.5068</v>
+        <v>5.9649</v>
       </c>
       <c r="N9" t="n">
         <v>152</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.8929</v>
+        <v>4.1034</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3456</v>
+        <v>1.4184</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1513</v>
+        <v>1.1909</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8929</v>
+        <v>4.1034</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4012</v>
+        <v>4.1034</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5083</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1465</v>
+        <v>4.1311</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1713</v>
+        <v>4.1659</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5083</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="L10" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.662999999999999</v>
+        <v>4.1659</v>
       </c>
       <c r="N10" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7755</v>
+        <v>4.0333</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3051</v>
+        <v>1.3942</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1039</v>
+        <v>1.163</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7755</v>
+        <v>4.0333</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7755</v>
+        <v>4.5416</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.5083</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7755</v>
+        <v>5.7116</v>
       </c>
       <c r="I11" t="n">
-        <v>3.793</v>
+        <v>4.6294</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.5083</v>
       </c>
       <c r="K11" t="n">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.793</v>
+        <v>4.1211</v>
       </c>
       <c r="N11" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12">
@@ -962,7 +962,7 @@
         <v>1.2609</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0523</v>
+        <v>1.0094</v>
       </c>
       <c r="E12" t="n">
         <v>3.6479</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1791</v>
+        <v>3.2008</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0989</v>
+        <v>1.1064</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8629</v>
+        <v>0.8313</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1791</v>
+        <v>3.2008</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6299</v>
+        <v>3.2008</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5492</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6299</v>
+        <v>3.2008</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1316</v>
+        <v>3.2277</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5492</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="L13" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6808</v>
+        <v>3.2277</v>
       </c>
       <c r="N13" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0574</v>
+        <v>3.1791</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0568</v>
+        <v>1.0989</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8138</v>
+        <v>0.8226</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0574</v>
+        <v>3.1791</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0574</v>
+        <v>2.6299</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.5492</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0574</v>
+        <v>2.6299</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0716</v>
+        <v>2.1316</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.5492</v>
       </c>
       <c r="K14" t="n">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0716</v>
+        <v>2.6808</v>
       </c>
       <c r="N14" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.834</v>
+        <v>3.0866</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9796</v>
+        <v>1.0669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7235</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.834</v>
+        <v>3.0866</v>
       </c>
       <c r="F15" t="n">
-        <v>2.013</v>
+        <v>3.567</v>
       </c>
       <c r="G15" t="n">
-        <v>0.821</v>
+        <v>-0.4804</v>
       </c>
       <c r="H15" t="n">
-        <v>2.013</v>
+        <v>3.567</v>
       </c>
       <c r="I15" t="n">
-        <v>2.013</v>
+        <v>3.567</v>
       </c>
       <c r="J15" t="n">
-        <v>0.821</v>
+        <v>-0.4804</v>
       </c>
       <c r="K15" t="n">
         <v>128</v>
@@ -1127,7 +1127,7 @@
         <v>76</v>
       </c>
       <c r="M15" t="n">
-        <v>2.834</v>
+        <v>3.0866</v>
       </c>
       <c r="N15" t="n">
         <v>204</v>
@@ -1136,768 +1136,768 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.631</v>
+        <v>2.834</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9094</v>
+        <v>0.9796</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6415</v>
+        <v>0.6852</v>
       </c>
       <c r="E16" t="n">
-        <v>2.631</v>
+        <v>2.834</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6081</v>
+        <v>2.013</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0229</v>
+        <v>0.821</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6081</v>
+        <v>2.013</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1139</v>
+        <v>2.013</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0229</v>
+        <v>0.821</v>
       </c>
       <c r="K16" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1368</v>
+        <v>2.834</v>
       </c>
       <c r="N16" t="n">
-        <v>152</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.316</v>
+        <v>2.6748</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8006</v>
+        <v>0.9246</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5143</v>
+        <v>0.6217</v>
       </c>
       <c r="E17" t="n">
-        <v>2.316</v>
+        <v>2.6748</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7964</v>
+        <v>3.1886</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4804</v>
+        <v>-0.5138</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7964</v>
+        <v>3.1886</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7964</v>
+        <v>3.1886</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4804</v>
+        <v>-0.5138</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L17" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>2.316</v>
+        <v>2.6748</v>
       </c>
       <c r="N17" t="n">
-        <v>204</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>riskyb0b</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.077</v>
+        <v>2.6747</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7179</v>
+        <v>0.9245</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4177</v>
+        <v>0.6217</v>
       </c>
       <c r="E18" t="n">
-        <v>2.077</v>
+        <v>2.6747</v>
       </c>
       <c r="F18" t="n">
-        <v>2.077</v>
+        <v>2.6518</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0229</v>
       </c>
       <c r="H18" t="n">
-        <v>2.077</v>
+        <v>2.6518</v>
       </c>
       <c r="I18" t="n">
-        <v>2.077</v>
+        <v>2.1493</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0229</v>
       </c>
       <c r="K18" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>2.077</v>
+        <v>2.1722</v>
       </c>
       <c r="N18" t="n">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>riskyb0b</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0558</v>
+        <v>2.077</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7106</v>
+        <v>0.7179</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4091</v>
+        <v>0.3836</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0558</v>
+        <v>2.077</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4382</v>
+        <v>2.077</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6176</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4382</v>
+        <v>2.077</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1657</v>
+        <v>2.077</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6176</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="L19" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7833</v>
+        <v>2.077</v>
       </c>
       <c r="N19" t="n">
-        <v>152</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0506</v>
+        <v>2.0558</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7088</v>
+        <v>0.7106</v>
       </c>
       <c r="D20" t="n">
-        <v>0.407</v>
+        <v>0.3751</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0506</v>
+        <v>2.0558</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4609</v>
+        <v>1.4382</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4103</v>
+        <v>0.6176</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4609</v>
+        <v>1.4382</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9946</v>
+        <v>1.1657</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4103</v>
+        <v>0.6176</v>
       </c>
       <c r="K20" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L20" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5843</v>
+        <v>1.7833</v>
       </c>
       <c r="N20" t="n">
-        <v>246</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>khaN</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9937</v>
+        <v>2.0506</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6891</v>
+        <v>0.7088</v>
       </c>
       <c r="D21" t="n">
-        <v>0.384</v>
+        <v>0.373</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9937</v>
+        <v>2.0506</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9937</v>
+        <v>2.4609</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.4103</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9937</v>
+        <v>2.4609</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9937</v>
+        <v>1.9946</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.4103</v>
       </c>
       <c r="K21" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9937</v>
+        <v>1.5843</v>
       </c>
       <c r="N21" t="n">
-        <v>113</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>khaN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.964</v>
+        <v>1.9937</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6891</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3721</v>
+        <v>0.3504</v>
       </c>
       <c r="E22" t="n">
-        <v>1.964</v>
+        <v>1.9937</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5142</v>
+        <v>1.9937</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4498</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5142</v>
+        <v>1.9937</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4168</v>
+        <v>1.9937</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4498</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="L22" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8666</v>
+        <v>1.9937</v>
       </c>
       <c r="N22" t="n">
-        <v>246</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7502</v>
+        <v>1.964</v>
       </c>
       <c r="C23" t="n">
-        <v>0.605</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2857</v>
+        <v>0.3385</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7502</v>
+        <v>1.964</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4609</v>
+        <v>0.5142</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2893</v>
+        <v>1.4498</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4609</v>
+        <v>0.5142</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4674</v>
+        <v>0.4168</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2893</v>
+        <v>1.4498</v>
       </c>
       <c r="K23" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="L23" t="n">
         <v>106</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7567</v>
+        <v>1.8666</v>
       </c>
       <c r="N23" t="n">
-        <v>290</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7441</v>
+        <v>1.7451</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6029</v>
+        <v>0.6032</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2832</v>
+        <v>0.2513</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7441</v>
+        <v>1.7451</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2579</v>
+        <v>0.4558</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5138</v>
+        <v>1.2893</v>
       </c>
       <c r="H24" t="n">
-        <v>2.2579</v>
+        <v>0.4558</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2579</v>
+        <v>0.4674</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5138</v>
+        <v>1.2893</v>
       </c>
       <c r="K24" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="L24" t="n">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7441</v>
+        <v>1.7567</v>
       </c>
       <c r="N24" t="n">
-        <v>169</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6694</v>
+        <v>1.6787</v>
       </c>
       <c r="C25" t="n">
-        <v>0.577</v>
+        <v>0.5803</v>
       </c>
       <c r="D25" t="n">
-        <v>0.253</v>
+        <v>0.2249</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6694</v>
+        <v>1.6787</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6694</v>
+        <v>2.2095</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.5308</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6694</v>
+        <v>2.2095</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6694</v>
+        <v>2.2095</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.5308</v>
       </c>
       <c r="K25" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6694</v>
+        <v>1.6787</v>
       </c>
       <c r="N25" t="n">
-        <v>113</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6624</v>
+        <v>1.6694</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5746</v>
+        <v>0.577</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2502</v>
+        <v>0.2212</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6624</v>
+        <v>1.6694</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6624</v>
+        <v>1.6694</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6624</v>
+        <v>1.6694</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6701</v>
+        <v>1.6694</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6701</v>
+        <v>1.6694</v>
       </c>
       <c r="N26" t="n">
-        <v>192</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5735</v>
+        <v>1.6562</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5725</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2143</v>
+        <v>0.2159</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5735</v>
+        <v>1.6562</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5735</v>
+        <v>1.6562</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5735</v>
+        <v>1.6562</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5735</v>
+        <v>1.6701</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.5735</v>
+        <v>1.6701</v>
       </c>
       <c r="N27" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1eeR</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5587</v>
+        <v>1.5735</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2083</v>
+        <v>0.183</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5587</v>
+        <v>1.5735</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5587</v>
+        <v>1.5735</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5587</v>
+        <v>1.5735</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5587</v>
+        <v>1.5735</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5587</v>
+        <v>1.5735</v>
       </c>
       <c r="N28" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>1eeR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5485</v>
+        <v>1.5587</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5353</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2042</v>
+        <v>0.1771</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5485</v>
+        <v>1.5587</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5485</v>
+        <v>1.5587</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5485</v>
+        <v>1.5587</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5557</v>
+        <v>1.5587</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5557</v>
+        <v>1.5587</v>
       </c>
       <c r="N29" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5293</v>
+        <v>1.5459</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5286</v>
+        <v>0.5344</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1964</v>
+        <v>0.172</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5293</v>
+        <v>1.5459</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0601</v>
+        <v>1.5459</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5308</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0601</v>
+        <v>1.5459</v>
       </c>
       <c r="I30" t="n">
-        <v>2.0601</v>
+        <v>1.5459</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5308</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="L30" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5293</v>
+        <v>1.5459</v>
       </c>
       <c r="N30" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4455</v>
+        <v>1.5427</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4997</v>
+        <v>0.5333</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1626</v>
+        <v>0.1707</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4455</v>
+        <v>1.5427</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4455</v>
+        <v>1.5427</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4455</v>
+        <v>1.5427</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4455</v>
+        <v>1.5557</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4455</v>
+        <v>1.5557</v>
       </c>
       <c r="N31" t="n">
-        <v>92</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3708</v>
+        <v>1.4455</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4738</v>
+        <v>0.4997</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1324</v>
+        <v>0.132</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3708</v>
+        <v>1.4455</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3708</v>
+        <v>1.4455</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3708</v>
+        <v>1.4455</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3708</v>
+        <v>1.4455</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3708</v>
+        <v>1.4455</v>
       </c>
       <c r="N32" t="n">
         <v>92</v>
@@ -1918,78 +1918,78 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2811</v>
+        <v>1.3708</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4428</v>
+        <v>0.4738</v>
       </c>
       <c r="D33" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1022</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2811</v>
+        <v>1.3708</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2811</v>
+        <v>1.3708</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2811</v>
+        <v>1.3708</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2811</v>
+        <v>1.3708</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2811</v>
+        <v>1.3708</v>
       </c>
       <c r="N33" t="n">
-        <v>157</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2781</v>
+        <v>1.2811</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4418</v>
+        <v>0.4428</v>
       </c>
       <c r="D34" t="n">
-        <v>0.095</v>
+        <v>0.0665</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2781</v>
+        <v>1.2811</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2781</v>
+        <v>1.2811</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2781</v>
+        <v>1.2811</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2781</v>
+        <v>1.2811</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2781</v>
+        <v>1.2811</v>
       </c>
       <c r="N34" t="n">
         <v>157</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0744</v>
+        <v>1.271</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3714</v>
+        <v>0.4393</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0127</v>
+        <v>0.0625</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0744</v>
+        <v>1.271</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0744</v>
+        <v>1.271</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0744</v>
+        <v>1.271</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0744</v>
+        <v>1.2817</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0744</v>
+        <v>1.2817</v>
       </c>
       <c r="N35" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9893</v>
+        <v>1.0744</v>
       </c>
       <c r="C36" t="n">
-        <v>0.342</v>
+        <v>0.3714</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0217</v>
+        <v>-0.0159</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9893</v>
+        <v>1.0744</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9893</v>
+        <v>1.0744</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9893</v>
+        <v>1.0744</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9939</v>
+        <v>1.0744</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9939</v>
+        <v>1.0744</v>
       </c>
       <c r="N36" t="n">
-        <v>192</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37">
@@ -2112,7 +2112,7 @@
         <v>0.3146</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0537</v>
+        <v>-0.0813</v>
       </c>
       <c r="E37" t="n">
         <v>0.9101</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8784</v>
+        <v>0.8951</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3036</v>
+        <v>0.3094</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0665</v>
+        <v>-0.0873</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8784</v>
+        <v>0.8951</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8784</v>
+        <v>0.8951</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8784</v>
+        <v>0.8951</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8784</v>
+        <v>0.8951</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8784</v>
+        <v>0.8951</v>
       </c>
       <c r="N38" t="n">
         <v>63</v>
@@ -2194,645 +2194,645 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8353</v>
+        <v>0.8595</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2887</v>
+        <v>0.2971</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0839</v>
+        <v>-0.1015</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8353</v>
+        <v>0.8595</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8353</v>
+        <v>0.8595</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8353</v>
+        <v>0.8595</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8353</v>
+        <v>0.8595</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8353</v>
+        <v>0.8595</v>
       </c>
       <c r="N39" t="n">
-        <v>92</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6866</v>
+        <v>0.8353</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2373</v>
+        <v>0.2887</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.144</v>
+        <v>-0.1111</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6866</v>
+        <v>0.8353</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6866</v>
+        <v>0.8353</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6866</v>
+        <v>0.8353</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6866</v>
+        <v>0.8353</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6866</v>
+        <v>0.8353</v>
       </c>
       <c r="N40" t="n">
-        <v>157</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.518</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1791</v>
+        <v>0.2465</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2121</v>
+        <v>-0.1598</v>
       </c>
       <c r="E41" t="n">
-        <v>0.518</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.518</v>
+        <v>1.6083</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.8951</v>
       </c>
       <c r="H41" t="n">
-        <v>0.518</v>
+        <v>1.6083</v>
       </c>
       <c r="I41" t="n">
-        <v>0.518</v>
+        <v>1.6083</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.8951</v>
       </c>
       <c r="K41" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M41" t="n">
-        <v>0.518</v>
+        <v>0.7132000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>68</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1782</v>
+        <v>0.2304</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2131</v>
+        <v>-0.1784</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="N42" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4559</v>
+        <v>0.6499</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1576</v>
+        <v>0.2246</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2372</v>
+        <v>-0.185</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4559</v>
+        <v>0.6499</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4559</v>
+        <v>1.2844</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.6345</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4559</v>
+        <v>1.2844</v>
       </c>
       <c r="I43" t="n">
-        <v>0.458</v>
+        <v>1.3171</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.6345</v>
       </c>
       <c r="K43" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M43" t="n">
-        <v>0.458</v>
+        <v>0.6826</v>
       </c>
       <c r="N43" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3959</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1368</v>
+        <v>0.1782</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2614</v>
+        <v>-0.2385</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3959</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3959</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3959</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3959</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3959</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3669</v>
+        <v>0.4542</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1268</v>
+        <v>0.157</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2731</v>
+        <v>-0.263</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3669</v>
+        <v>0.4542</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0014</v>
+        <v>0.4542</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.6345</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0014</v>
+        <v>0.4542</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0154</v>
+        <v>0.458</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.6345</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="L45" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3809000000000001</v>
+        <v>0.458</v>
       </c>
       <c r="N45" t="n">
-        <v>290</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3618</v>
+        <v>0.3959</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1251</v>
+        <v>0.1368</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2752</v>
+        <v>-0.2862</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3618</v>
+        <v>0.3959</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3618</v>
+        <v>0.3959</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3618</v>
+        <v>0.3959</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3618</v>
+        <v>0.3959</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3618</v>
+        <v>0.3959</v>
       </c>
       <c r="N46" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2154</v>
+        <v>0.3618</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0745</v>
+        <v>0.1251</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3343</v>
+        <v>-0.2998</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2154</v>
+        <v>0.3618</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2154</v>
+        <v>0.3618</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2154</v>
+        <v>0.3618</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2154</v>
+        <v>0.3618</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2154</v>
+        <v>0.3618</v>
       </c>
       <c r="N47" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0989</v>
+        <v>0.2154</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0342</v>
+        <v>0.0745</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3814</v>
+        <v>-0.3581</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0989</v>
+        <v>0.2154</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0989</v>
+        <v>0.2154</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0989</v>
+        <v>0.2154</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0989</v>
+        <v>0.2154</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0989</v>
+        <v>0.2154</v>
       </c>
       <c r="N48" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0847</v>
+        <v>0.1204</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0293</v>
+        <v>0.0416</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3871</v>
+        <v>-0.3959</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0847</v>
+        <v>0.1204</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0847</v>
+        <v>-0.3522</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.4726</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0847</v>
+        <v>-0.3522</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0847</v>
+        <v>-0.3522</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.4726</v>
       </c>
       <c r="K49" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M49" t="n">
-        <v>0.0847</v>
+        <v>0.1204</v>
       </c>
       <c r="N49" t="n">
-        <v>63</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0669</v>
+        <v>0.0989</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0231</v>
+        <v>0.0342</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4484</v>
+        <v>-0.4045</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0669</v>
+        <v>0.0989</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.5395</v>
+        <v>0.0989</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4726</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.5395</v>
+        <v>0.0989</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5395</v>
+        <v>0.0989</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4726</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="L50" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.06689999999999996</v>
+        <v>0.0989</v>
       </c>
       <c r="N50" t="n">
-        <v>204</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HUASOPEEK</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0925</v>
+        <v>0.0847</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.032</v>
+        <v>0.0293</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4587</v>
+        <v>-0.4102</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0925</v>
+        <v>0.0847</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0925</v>
+        <v>0.0847</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0925</v>
+        <v>0.0847</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0925</v>
+        <v>0.0847</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0925</v>
+        <v>0.0847</v>
       </c>
       <c r="N51" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>HUASOPEEK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1781</v>
+        <v>-0.0925</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0616</v>
+        <v>-0.032</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4933</v>
+        <v>-0.4808</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1781</v>
+        <v>-0.0925</v>
       </c>
       <c r="F52" t="n">
-        <v>0.717</v>
+        <v>-0.0925</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.8951</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.717</v>
+        <v>-0.0925</v>
       </c>
       <c r="I52" t="n">
-        <v>0.717</v>
+        <v>-0.0925</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.8951</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="L52" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1781</v>
+        <v>-0.0925</v>
       </c>
       <c r="N52" t="n">
-        <v>169</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53">
@@ -2848,7 +2848,7 @@
         <v>-0.0687</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5017</v>
+        <v>-0.5231</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1988</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0687</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5017</v>
+        <v>-0.5231</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1988</v>
@@ -2940,7 +2940,7 @@
         <v>-0.07140000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5049</v>
+        <v>-0.5263</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2067</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2636</v>
+        <v>-0.2626</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0911</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5279</v>
+        <v>-0.5485</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2636</v>
+        <v>-0.2626</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2636</v>
+        <v>-0.2626</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2636</v>
+        <v>-0.2626</v>
       </c>
       <c r="I56" t="n">
         <v>-0.2648</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1141</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5547</v>
+        <v>-0.5754</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3301</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1152</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.556</v>
+        <v>-0.5767</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3334</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1883</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6414</v>
+        <v>-0.6609</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5447</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2531</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.7357</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7323</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7983</v>
+        <v>-0.7953</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2759</v>
+        <v>-0.2749</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7439</v>
+        <v>-0.7608</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7983</v>
+        <v>-0.7953</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7983</v>
+        <v>-0.7953</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7983</v>
+        <v>-0.7953</v>
       </c>
       <c r="I61" t="n">
         <v>-0.802</v>
@@ -3262,7 +3262,7 @@
         <v>-0.312</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.786</v>
+        <v>-0.8035</v>
       </c>
       <c r="E62" t="n">
         <v>-0.9025</v>
@@ -3308,7 +3308,7 @@
         <v>-0.347</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.827</v>
+        <v>-0.8439</v>
       </c>
       <c r="E63" t="n">
         <v>-1.004</v>
@@ -3344,170 +3344,170 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Xant3r</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1109</v>
+        <v>-1.1061</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.384</v>
+        <v>-0.3823</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8701</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.1109</v>
+        <v>-1.1061</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.1109</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.4362</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.1109</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.1109</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.4362</v>
       </c>
       <c r="K64" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M64" t="n">
-        <v>-1.1109</v>
+        <v>-1.1061</v>
       </c>
       <c r="N64" t="n">
-        <v>113</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SLIGHT</t>
+          <t>Xant3r</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1836</v>
+        <v>-1.1109</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4091</v>
+        <v>-0.384</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8995</v>
+        <v>-0.8865</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.1836</v>
+        <v>-1.1109</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.1836</v>
+        <v>-1.1109</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.1836</v>
+        <v>-1.1109</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.1836</v>
+        <v>-1.1109</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.1836</v>
+        <v>-1.1109</v>
       </c>
       <c r="N65" t="n">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>xiaosaGe</t>
+          <t>SLIGHT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.2076</v>
+        <v>-1.1836</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4174</v>
+        <v>-0.4091</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9092</v>
+        <v>-0.9155</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.2076</v>
+        <v>-1.1836</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.2076</v>
+        <v>-1.1836</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.2076</v>
+        <v>-1.1836</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.2076</v>
+        <v>-1.1836</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.2076</v>
+        <v>-1.1836</v>
       </c>
       <c r="N66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>18yM</t>
+          <t>xiaosaGe</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.2396</v>
+        <v>-1.2076</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4285</v>
+        <v>-0.4174</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9221</v>
+        <v>-0.925</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2396</v>
+        <v>-1.2076</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.2396</v>
+        <v>-1.2076</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.2396</v>
+        <v>-1.2076</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.2396</v>
+        <v>-1.2076</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.2396</v>
+        <v>-1.2076</v>
       </c>
       <c r="N67" t="n">
         <v>48</v>
@@ -3528,47 +3528,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>18yM</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2959</v>
+        <v>-1.2396</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4479</v>
+        <v>-0.4285</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9449</v>
+        <v>-0.9378</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2959</v>
+        <v>-1.2396</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8597</v>
+        <v>-1.2396</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.4362</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8597</v>
+        <v>-1.2396</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8597</v>
+        <v>-1.2396</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.4362</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="L68" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.2959</v>
+        <v>-1.2396</v>
       </c>
       <c r="N68" t="n">
-        <v>169</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
@@ -3584,7 +3584,7 @@
         <v>-0.4495</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9467</v>
+        <v>-0.962</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3003</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.3153</v>
+        <v>-1.3104</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4547</v>
+        <v>-0.453</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9527</v>
+        <v>-0.966</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3153</v>
+        <v>-1.3104</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.3153</v>
+        <v>-1.3104</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.3153</v>
+        <v>-1.3104</v>
       </c>
       <c r="I70" t="n">
         <v>-1.3214</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4995</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0051</v>
+        <v>-1.0196</v>
       </c>
       <c r="E71" t="n">
         <v>-1.445</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5016</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0075</v>
+        <v>-1.022</v>
       </c>
       <c r="E72" t="n">
         <v>-1.451</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5057</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0123</v>
+        <v>-1.0267</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4629</v>
@@ -3814,7 +3814,7 @@
         <v>-0.5346</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0462</v>
+        <v>-1.0601</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5467</v>
@@ -3860,7 +3860,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0759</v>
+        <v>-1.0894</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6202</v>
@@ -3906,7 +3906,7 @@
         <v>-0.5659999999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0828</v>
+        <v>-1.0963</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6374</v>
@@ -3952,7 +3952,7 @@
         <v>-0.678</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2137</v>
+        <v>-1.2253</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9614</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.0666</v>
+        <v>-2.0736</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7143</v>
+        <v>-0.7168</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2562</v>
+        <v>-1.27</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.0666</v>
+        <v>-2.0736</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9334</v>
+        <v>0.9264</v>
       </c>
       <c r="G78" t="n">
         <v>-3</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9334</v>
+        <v>0.9264</v>
       </c>
       <c r="I78" t="n">
         <v>0.9421</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.1273</v>
+        <v>-2.1194</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7353</v>
+        <v>-0.7326</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2807</v>
+        <v>-1.2883</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.1273</v>
+        <v>-2.1194</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.1273</v>
+        <v>-2.1194</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.1273</v>
+        <v>-2.1194</v>
       </c>
       <c r="I79" t="n">
         <v>-2.1372</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-4.2088</v>
+        <v>-4.173</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.4548</v>
+        <v>-1.4425</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.1216</v>
+        <v>-2.1064</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.2088</v>
+        <v>-4.173</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.2104</v>
+        <v>-3.1746</v>
       </c>
       <c r="G80" t="n">
         <v>-0.9984</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.2104</v>
+        <v>-3.1746</v>
       </c>
       <c r="I80" t="n">
         <v>-3.2554</v>
@@ -4136,7 +4136,7 @@
         <v>-2.1817</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.9711</v>
+        <v>-2.9585</v>
       </c>
       <c r="E81" t="n">
         <v>-6.3116</v>

--- a/database/event/7437/event_7437_evp_summary.xlsx
+++ b/database/event/7437/event_7437_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8829</v>
+        <v>7.134</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3792</v>
+        <v>2.466</v>
       </c>
       <c r="D2" t="n">
-        <v>2.509</v>
+        <v>2.5728</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8829</v>
+        <v>7.134</v>
       </c>
       <c r="F2" t="n">
         <v>4.4037</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8514</v>
+        <v>7.077</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3683</v>
+        <v>2.4463</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4947</v>
+        <v>2.5473</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8514</v>
+        <v>7.077</v>
       </c>
       <c r="F3" t="n">
         <v>3.5976</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3443</v>
+        <v>6.5075</v>
       </c>
       <c r="C4" t="n">
-        <v>2.193</v>
+        <v>2.2494</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2639</v>
+        <v>2.2929</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3443</v>
+        <v>6.5075</v>
       </c>
       <c r="F4" t="n">
         <v>1.81</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5285</v>
+        <v>5.683</v>
       </c>
       <c r="C5" t="n">
-        <v>1.911</v>
+        <v>1.9644</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8925</v>
+        <v>1.9247</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5285</v>
+        <v>5.683</v>
       </c>
       <c r="F5" t="n">
         <v>2.7864</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4338</v>
+        <v>5.3252</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8783</v>
+        <v>1.8407</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8494</v>
+        <v>1.7648</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4338</v>
+        <v>5.3252</v>
       </c>
       <c r="F6" t="n">
         <v>2.3498</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8543</v>
+        <v>4.939</v>
       </c>
       <c r="C7" t="n">
-        <v>1.678</v>
+        <v>1.7072</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5856</v>
+        <v>1.5923</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8543</v>
+        <v>4.939</v>
       </c>
       <c r="F7" t="n">
         <v>4.5807</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7332</v>
+        <v>4.8124</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6361</v>
+        <v>1.6635</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5304</v>
+        <v>1.5358</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7332</v>
+        <v>4.8124</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8404</v>
+        <v>3.2172</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8928</v>
+        <v>1.4633</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4919</v>
+        <v>4.3164</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6742</v>
+        <v>4.6588</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8928</v>
+        <v>1.4633</v>
       </c>
       <c r="K8" t="n">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="L8" t="n">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>5.567</v>
+        <v>6.122100000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>318</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6805</v>
+        <v>4.8035</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6179</v>
+        <v>1.6604</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5065</v>
+        <v>1.5318</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6805</v>
+        <v>4.8035</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2172</v>
+        <v>2.8404</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4633</v>
+        <v>1.8928</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3164</v>
+        <v>3.4919</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6588</v>
+        <v>3.6742</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4633</v>
+        <v>1.8928</v>
       </c>
       <c r="K9" t="n">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="L9" t="n">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="M9" t="n">
-        <v>6.122100000000001</v>
+        <v>5.567</v>
       </c>
       <c r="N9" t="n">
-        <v>290</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9258</v>
+        <v>3.9667</v>
       </c>
       <c r="C10" t="n">
-        <v>1.357</v>
+        <v>1.3711</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1629</v>
+        <v>1.158</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9258</v>
+        <v>3.9667</v>
       </c>
       <c r="F10" t="n">
         <v>2.5961</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7767</v>
+        <v>3.8718</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3055</v>
+        <v>1.3383</v>
       </c>
       <c r="D11" t="n">
-        <v>1.095</v>
+        <v>1.1156</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7767</v>
+        <v>3.8718</v>
       </c>
       <c r="F11" t="n">
         <v>4.0389</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6133</v>
+        <v>3.6694</v>
       </c>
       <c r="C12" t="n">
-        <v>1.249</v>
+        <v>1.2684</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0206</v>
+        <v>1.0252</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6133</v>
+        <v>3.6694</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9551</v>
+        <v>3.3807</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6582</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8556</v>
+        <v>4.6743</v>
       </c>
       <c r="I12" t="n">
-        <v>2.622</v>
+        <v>4.7948</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6582</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="L12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2802</v>
+        <v>4.7948</v>
       </c>
       <c r="N12" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3852</v>
+        <v>3.6681</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1701</v>
+        <v>1.2679</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9167999999999999</v>
+        <v>1.0246</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3852</v>
+        <v>3.6681</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5854</v>
+        <v>2.9551</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7998</v>
+        <v>0.6582</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9338</v>
+        <v>4.8556</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9338</v>
+        <v>2.622</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7998</v>
+        <v>0.6582</v>
       </c>
       <c r="K13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="L13" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7336</v>
+        <v>3.2802</v>
       </c>
       <c r="N13" t="n">
-        <v>204</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3815</v>
+        <v>3.3686</v>
       </c>
       <c r="C14" t="n">
-        <v>1.1689</v>
+        <v>1.1644</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9151</v>
+        <v>0.8909</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3815</v>
+        <v>3.3686</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3815</v>
+        <v>2.5854</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.7998</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6761</v>
+        <v>2.9338</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7966</v>
+        <v>2.9338</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.7998</v>
       </c>
       <c r="K14" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7966</v>
+        <v>3.7336</v>
       </c>
       <c r="N14" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1261</v>
+        <v>3.2131</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0806</v>
+        <v>1.1106</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8214</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1261</v>
+        <v>3.2131</v>
       </c>
       <c r="F15" t="n">
         <v>3.1261</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0145</v>
+        <v>2.9013</v>
       </c>
       <c r="C16" t="n">
-        <v>1.042</v>
+        <v>1.0029</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7481</v>
+        <v>0.6821</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0145</v>
+        <v>2.9013</v>
       </c>
       <c r="F16" t="n">
         <v>2.8993</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8553</v>
+        <v>2.8697</v>
       </c>
       <c r="C17" t="n">
-        <v>0.987</v>
+        <v>0.9919</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6756</v>
+        <v>0.668</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8553</v>
+        <v>2.8697</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3527</v>
+        <v>2.9196</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5026</v>
+        <v>-0.2444</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8682</v>
+        <v>3.6652</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5488</v>
+        <v>3.6652</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5026</v>
+        <v>-0.2444</v>
       </c>
       <c r="K17" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0514</v>
+        <v>3.4208</v>
       </c>
       <c r="N17" t="n">
-        <v>152</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6752</v>
+        <v>2.7916</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9247</v>
+        <v>0.965</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5936</v>
+        <v>0.6331</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6752</v>
+        <v>2.7916</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9196</v>
+        <v>1.2782</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2444</v>
+        <v>1.3341</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6652</v>
+        <v>1.2782</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6652</v>
+        <v>0.6902</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2444</v>
+        <v>1.3341</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="L18" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4208</v>
+        <v>2.0243</v>
       </c>
       <c r="N18" t="n">
-        <v>204</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6123</v>
+        <v>2.7349</v>
       </c>
       <c r="C19" t="n">
-        <v>0.903</v>
+        <v>0.9454</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6078</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6123</v>
+        <v>2.7349</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2782</v>
+        <v>2.3527</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3341</v>
+        <v>0.5026</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2782</v>
+        <v>2.8682</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6902</v>
+        <v>1.5488</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3341</v>
+        <v>0.5026</v>
       </c>
       <c r="K19" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L19" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0243</v>
+        <v>2.0514</v>
       </c>
       <c r="N19" t="n">
-        <v>246</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5817</v>
+        <v>2.7168</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8924</v>
+        <v>0.9391</v>
       </c>
       <c r="D20" t="n">
-        <v>0.551</v>
+        <v>0.5997</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5817</v>
+        <v>2.7168</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5817</v>
+        <v>2.577</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9256</v>
+        <v>2.9153</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9256</v>
+        <v>2.9153</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9256</v>
+        <v>2.9153</v>
       </c>
       <c r="N20" t="n">
         <v>113</v>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.4988</v>
+        <v>2.6447</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8637</v>
+        <v>0.9142</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5133</v>
+        <v>0.5675</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4988</v>
+        <v>2.6447</v>
       </c>
       <c r="F21" t="n">
         <v>2.8725</v>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.3935</v>
+        <v>2.5164</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8273</v>
+        <v>0.8698</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4654</v>
+        <v>0.5102</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3935</v>
+        <v>2.5164</v>
       </c>
       <c r="F22" t="n">
         <v>2.3935</v>
@@ -1458,461 +1458,461 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>riskyb0b</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.3861</v>
+        <v>2.5138</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8248</v>
+        <v>0.8689</v>
       </c>
       <c r="D23" t="n">
-        <v>0.462</v>
+        <v>0.509</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3861</v>
+        <v>2.5138</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3861</v>
+        <v>2.3762</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4976</v>
+        <v>2.4759</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4976</v>
+        <v>2.4759</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.4976</v>
+        <v>2.4759</v>
       </c>
       <c r="N23" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>riskyb0b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3723</v>
+        <v>2.4628</v>
       </c>
       <c r="C24" t="n">
-        <v>0.82</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4557</v>
+        <v>0.4863</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3723</v>
+        <v>2.4628</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3723</v>
+        <v>2.3862</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4674</v>
+        <v>2.4978</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4674</v>
+        <v>2.4978</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.4674</v>
+        <v>2.4978</v>
       </c>
       <c r="N24" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>khaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2912</v>
+        <v>2.3301</v>
       </c>
       <c r="C25" t="n">
-        <v>0.792</v>
+        <v>0.8054</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4188</v>
+        <v>0.427</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2912</v>
+        <v>2.3301</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1755</v>
+        <v>2.275</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1157</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1755</v>
+        <v>2.275</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2687</v>
+        <v>2.275</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1157</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="L25" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.3844</v>
+        <v>2.275</v>
       </c>
       <c r="N25" t="n">
-        <v>290</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>khaN</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.2748</v>
+        <v>2.2683</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7863</v>
+        <v>0.7841</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4113</v>
+        <v>0.3994</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2748</v>
+        <v>2.2683</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2748</v>
+        <v>1.1755</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.1157</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2748</v>
+        <v>1.1755</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2748</v>
+        <v>1.2687</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.1157</v>
       </c>
       <c r="K26" t="n">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2748</v>
+        <v>2.3844</v>
       </c>
       <c r="N26" t="n">
-        <v>113</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2251</v>
+        <v>2.0465</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7691</v>
+        <v>0.7074</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3887</v>
+        <v>0.3003</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2251</v>
+        <v>2.0465</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6733</v>
+        <v>2.3314</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4482</v>
+        <v>-0.4078</v>
       </c>
       <c r="H27" t="n">
-        <v>3.926</v>
+        <v>2.3778</v>
       </c>
       <c r="I27" t="n">
-        <v>2.12</v>
+        <v>2.3778</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4482</v>
+        <v>-0.4078</v>
       </c>
       <c r="K27" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="L27" t="n">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6718</v>
+        <v>1.97</v>
       </c>
       <c r="N27" t="n">
-        <v>246</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9236</v>
+        <v>2.0262</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6649</v>
+        <v>0.7004</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2515</v>
+        <v>0.2912</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9236</v>
+        <v>2.0262</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3314</v>
+        <v>2.6733</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4078</v>
+        <v>-0.4482</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3778</v>
+        <v>3.926</v>
       </c>
       <c r="I28" t="n">
-        <v>2.3778</v>
+        <v>2.12</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4078</v>
+        <v>-0.4482</v>
       </c>
       <c r="K28" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="M28" t="n">
-        <v>1.97</v>
+        <v>1.6718</v>
       </c>
       <c r="N28" t="n">
-        <v>169</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1eeR</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8817</v>
+        <v>1.9357</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6504</v>
+        <v>0.6691</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2324</v>
+        <v>0.2508</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8817</v>
+        <v>1.9357</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8817</v>
+        <v>1.843</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8817</v>
+        <v>1.843</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8817</v>
+        <v>1.8905</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.8817</v>
+        <v>1.8905</v>
       </c>
       <c r="N29" t="n">
-        <v>113</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8441</v>
+        <v>1.912</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6374</v>
+        <v>0.6609</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2153</v>
+        <v>0.2402</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8441</v>
+        <v>1.912</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8441</v>
+        <v>1.8093</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8441</v>
+        <v>1.8093</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8916</v>
+        <v>1.8093</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.8916</v>
+        <v>1.8093</v>
       </c>
       <c r="N30" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>1eeR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8093</v>
+        <v>1.885</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6254</v>
+        <v>0.6516</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1994</v>
+        <v>0.2282</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8093</v>
+        <v>1.885</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8093</v>
+        <v>1.8821</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8093</v>
+        <v>1.8821</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8093</v>
+        <v>1.8821</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8093</v>
+        <v>1.8821</v>
       </c>
       <c r="N31" t="n">
-        <v>157</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7021</v>
+        <v>1.7897</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5884</v>
+        <v>0.6186</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1506</v>
+        <v>0.1856</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7021</v>
+        <v>1.7897</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7021</v>
+        <v>1.6714</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7021</v>
+        <v>1.6714</v>
       </c>
       <c r="I32" t="n">
-        <v>1.746</v>
+        <v>1.6714</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.746</v>
+        <v>1.6714</v>
       </c>
       <c r="N32" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6989</v>
+        <v>1.7628</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6093</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1492</v>
+        <v>0.1736</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6989</v>
+        <v>1.7628</v>
       </c>
       <c r="F33" t="n">
         <v>1.6989</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.6714</v>
+        <v>1.7579</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5777</v>
+        <v>0.6076</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1367</v>
+        <v>0.1714</v>
       </c>
       <c r="E34" t="n">
-        <v>1.6714</v>
+        <v>1.7579</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6714</v>
+        <v>1.7138</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.6714</v>
+        <v>1.7138</v>
       </c>
       <c r="I34" t="n">
-        <v>1.6714</v>
+        <v>1.758</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.6714</v>
+        <v>1.758</v>
       </c>
       <c r="N34" t="n">
-        <v>157</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.5762</v>
+        <v>1.6822</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5448</v>
+        <v>0.5815</v>
       </c>
       <c r="D35" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1376</v>
       </c>
       <c r="E35" t="n">
-        <v>1.5762</v>
+        <v>1.6822</v>
       </c>
       <c r="F35" t="n">
         <v>1.5762</v>
@@ -2056,78 +2056,78 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3568</v>
+        <v>1.4771</v>
       </c>
       <c r="C36" t="n">
-        <v>0.469</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0066</v>
+        <v>0.046</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3568</v>
+        <v>1.4771</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3568</v>
+        <v>1.1447</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3568</v>
+        <v>1.1447</v>
       </c>
       <c r="I36" t="n">
-        <v>1.3568</v>
+        <v>1.1447</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3568</v>
+        <v>1.1447</v>
       </c>
       <c r="N36" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.1919</v>
+        <v>1.3954</v>
       </c>
       <c r="C37" t="n">
-        <v>0.412</v>
+        <v>0.4823</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0095</v>
       </c>
       <c r="E37" t="n">
-        <v>1.1919</v>
+        <v>1.3954</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1919</v>
+        <v>1.3568</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1919</v>
+        <v>1.3568</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1919</v>
+        <v>1.3568</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1919</v>
+        <v>1.3568</v>
       </c>
       <c r="N37" t="n">
         <v>92</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1731</v>
+        <v>1.3105</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4055</v>
+        <v>0.453</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0902</v>
+        <v>-0.0284</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1731</v>
+        <v>1.3105</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1731</v>
+        <v>1.2261</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1731</v>
+        <v>1.2261</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1731</v>
+        <v>1.2261</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1731</v>
+        <v>1.2261</v>
       </c>
       <c r="N38" t="n">
         <v>106</v>
@@ -2194,277 +2194,277 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>buda</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.1595</v>
+        <v>1.1473</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4008</v>
+        <v>0.3966</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0964</v>
+        <v>-0.1013</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1595</v>
+        <v>1.1473</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1595</v>
+        <v>0.9445</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1595</v>
+        <v>0.9445</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1595</v>
+        <v>0.9445</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1595</v>
+        <v>0.9445</v>
       </c>
       <c r="N39" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0417</v>
+        <v>1.1348</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3601</v>
+        <v>0.3923</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.15</v>
+        <v>-0.1069</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0417</v>
+        <v>1.1348</v>
       </c>
       <c r="F40" t="n">
-        <v>1.691</v>
+        <v>1.1919</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6493</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.691</v>
+        <v>1.1919</v>
       </c>
       <c r="I40" t="n">
-        <v>1.691</v>
+        <v>1.1919</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6493</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="L40" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.0417</v>
+        <v>1.1919</v>
       </c>
       <c r="N40" t="n">
-        <v>169</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.0162</v>
+        <v>0.9758</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3513</v>
+        <v>0.3373</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1616</v>
+        <v>-0.178</v>
       </c>
       <c r="E41" t="n">
-        <v>1.0162</v>
+        <v>0.9758</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0162</v>
+        <v>1.691</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.6493</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0162</v>
+        <v>1.691</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0162</v>
+        <v>1.691</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.6493</v>
       </c>
       <c r="K41" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M41" t="n">
-        <v>1.0162</v>
+        <v>1.0417</v>
       </c>
       <c r="N41" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9873</v>
+        <v>0.9399</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3413</v>
+        <v>0.3249</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1748</v>
+        <v>-0.194</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9873</v>
+        <v>0.9399</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5784</v>
+        <v>1.0162</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.5911</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.5784</v>
+        <v>1.0162</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7036</v>
+        <v>1.0162</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.5911</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="L42" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1125</v>
+        <v>1.0162</v>
       </c>
       <c r="N42" t="n">
-        <v>290</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9751</v>
+        <v>0.9329</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3371</v>
+        <v>0.3225</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1803</v>
+        <v>-0.1971</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9751</v>
+        <v>0.9329</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9751</v>
+        <v>1.5784</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.5911</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9751</v>
+        <v>1.5784</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9751</v>
+        <v>1.7036</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.5911</v>
       </c>
       <c r="K43" t="n">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9751</v>
+        <v>1.1125</v>
       </c>
       <c r="N43" t="n">
-        <v>92</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>buda</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9445</v>
+        <v>0.8461</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3265</v>
+        <v>0.2925</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1942</v>
+        <v>-0.2359</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9445</v>
+        <v>0.8461</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9445</v>
+        <v>0.9751</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9445</v>
+        <v>0.9751</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9445</v>
+        <v>0.9751</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9445</v>
+        <v>0.9751</v>
       </c>
       <c r="N44" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="C45" t="n">
-        <v>0.28</v>
+        <v>0.2751</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2555</v>
+        <v>-0.2583</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="N45" t="n">
         <v>106</v>
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7548</v>
+        <v>0.6921</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2609</v>
+        <v>0.2392</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2806</v>
+        <v>-0.3047</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7548</v>
+        <v>0.6921</v>
       </c>
       <c r="F46" t="n">
         <v>0.7548</v>
@@ -2566,16 +2566,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5785</v>
+        <v>0.6852</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2</v>
+        <v>0.2368</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3609</v>
+        <v>-0.3078</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5785</v>
+        <v>0.6852</v>
       </c>
       <c r="F47" t="n">
         <v>0.5785</v>
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5371</v>
+        <v>0.5212</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1857</v>
+        <v>0.1802</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3797</v>
+        <v>-0.381</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5371</v>
+        <v>0.5212</v>
       </c>
       <c r="F48" t="n">
         <v>0.0597</v>
@@ -2654,124 +2654,124 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4219</v>
+        <v>0.4566</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1458</v>
+        <v>0.1578</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4321</v>
+        <v>-0.4099</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4219</v>
+        <v>0.4566</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4219</v>
+        <v>0.4694</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4219</v>
+        <v>0.4694</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4219</v>
+        <v>0.4694</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4219</v>
+        <v>0.4694</v>
       </c>
       <c r="N49" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4118</v>
+        <v>0.4111</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1423</v>
+        <v>0.1421</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4367</v>
+        <v>-0.4302</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4118</v>
+        <v>0.4111</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4118</v>
+        <v>0.288</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4118</v>
+        <v>0.288</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4118</v>
+        <v>0.288</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4118</v>
+        <v>0.288</v>
       </c>
       <c r="N50" t="n">
-        <v>106</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.2966</v>
+        <v>0.381</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1025</v>
+        <v>0.1317</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4892</v>
+        <v>-0.4436</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2966</v>
+        <v>0.381</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2966</v>
+        <v>0.4032</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2966</v>
+        <v>0.4032</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2966</v>
+        <v>0.4032</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2966</v>
+        <v>0.4032</v>
       </c>
       <c r="N51" t="n">
         <v>63</v>
@@ -2792,277 +2792,277 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2809</v>
+        <v>0.2346</v>
       </c>
       <c r="C52" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4963</v>
+        <v>-0.509</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2809</v>
+        <v>0.2346</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2809</v>
+        <v>-0.1978</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.4308</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2809</v>
+        <v>-0.1978</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2881</v>
+        <v>-0.1978</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>0.4308</v>
       </c>
       <c r="K52" t="n">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2881</v>
+        <v>0.233</v>
       </c>
       <c r="N52" t="n">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.233</v>
+        <v>0.1895</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0805</v>
+        <v>0.0655</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5181</v>
+        <v>-0.5292</v>
       </c>
       <c r="E53" t="n">
-        <v>0.233</v>
+        <v>0.1895</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1978</v>
+        <v>0.2196</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4308</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1978</v>
+        <v>0.2196</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1978</v>
+        <v>0.2196</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4308</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="L53" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.233</v>
+        <v>0.2196</v>
       </c>
       <c r="N53" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2196</v>
+        <v>0.1453</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0759</v>
+        <v>0.0502</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5242</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2196</v>
+        <v>0.1453</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2196</v>
+        <v>0.2809</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2196</v>
+        <v>0.2809</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2196</v>
+        <v>0.2881</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2196</v>
+        <v>0.2881</v>
       </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1964</v>
+        <v>0.0916</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0679</v>
+        <v>0.0317</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5729</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1964</v>
+        <v>0.0916</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1964</v>
+        <v>0.2335</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.1196</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1964</v>
+        <v>0.2335</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1964</v>
+        <v>0.2335</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.1196</v>
       </c>
       <c r="K55" t="n">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1964</v>
+        <v>0.1139</v>
       </c>
       <c r="N55" t="n">
-        <v>106</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1864</v>
+        <v>0.0599</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0644</v>
+        <v>0.0207</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5394</v>
+        <v>-0.5871</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1864</v>
+        <v>0.0599</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1864</v>
+        <v>0.1941</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1864</v>
+        <v>0.1941</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1864</v>
+        <v>0.1941</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1864</v>
+        <v>0.1941</v>
       </c>
       <c r="N56" t="n">
-        <v>157</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1139</v>
+        <v>0.037</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0394</v>
+        <v>0.0128</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5724</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1139</v>
+        <v>0.037</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2335</v>
+        <v>0.1864</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.1196</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2335</v>
+        <v>0.1864</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2335</v>
+        <v>0.1864</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.1196</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="L57" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1139</v>
+        <v>0.1864</v>
       </c>
       <c r="N57" t="n">
-        <v>204</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58">
@@ -3072,16 +3072,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.052</v>
+        <v>-0.0207</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.018</v>
+        <v>-0.0072</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6479</v>
+        <v>-0.6231</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.052</v>
+        <v>-0.0207</v>
       </c>
       <c r="F58" t="n">
         <v>-0.052</v>
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0864</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0282</v>
+        <v>-0.0299</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6614</v>
+        <v>-0.6524</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0864</v>
       </c>
       <c r="F59" t="n">
         <v>-0.08169999999999999</v>
@@ -3160,139 +3160,139 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>xiaosaGe</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1805</v>
+        <v>-0.1733</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0624</v>
+        <v>-0.0599</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7064</v>
+        <v>-0.6912</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1805</v>
+        <v>-0.1733</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1805</v>
+        <v>-0.7853</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1805</v>
+        <v>-0.7853</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1805</v>
+        <v>-0.7853</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1805</v>
+        <v>-0.7853</v>
       </c>
       <c r="N60" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.383</v>
+        <v>-0.3485</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1324</v>
+        <v>-0.1205</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7986</v>
+        <v>-0.7695</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.383</v>
+        <v>-0.3485</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.383</v>
+        <v>-0.1805</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.383</v>
+        <v>-0.1805</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3929</v>
+        <v>-0.1805</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3929</v>
+        <v>-0.1805</v>
       </c>
       <c r="N61" t="n">
-        <v>180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4309</v>
+        <v>-0.4979</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1489</v>
+        <v>-0.1721</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8204</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4309</v>
+        <v>-0.4979</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4309</v>
+        <v>-0.383</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4309</v>
+        <v>-0.383</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4309</v>
+        <v>-0.3929</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4309</v>
+        <v>-0.3929</v>
       </c>
       <c r="N62" t="n">
-        <v>48</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63">
@@ -3302,16 +3302,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4849</v>
+        <v>-0.5757</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1676</v>
+        <v>-0.199</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8449</v>
+        <v>-0.871</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4849</v>
+        <v>-0.5757</v>
       </c>
       <c r="F63" t="n">
         <v>-0.1416</v>
@@ -3344,415 +3344,415 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Xant3r</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.5124</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1771</v>
+        <v>-0.2002</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8575</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5124</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5124</v>
+        <v>-0.4309</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5124</v>
+        <v>-0.4309</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5124</v>
+        <v>-0.4309</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.5124</v>
+        <v>-0.4309</v>
       </c>
       <c r="N64" t="n">
-        <v>113</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>SLIGHT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7672</v>
+        <v>-0.6413</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2652</v>
+        <v>-0.2217</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9734</v>
+        <v>-0.9003</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7672</v>
+        <v>-0.6413</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7307</v>
+        <v>-1.0959</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0365</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7307</v>
+        <v>-1.0959</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7307</v>
+        <v>-1.0959</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.0365</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="L65" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7672</v>
+        <v>-1.0959</v>
       </c>
       <c r="N65" t="n">
-        <v>204</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>xiaosaGe</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7853</v>
+        <v>-0.6506</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2714</v>
+        <v>-0.2249</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9817</v>
+        <v>-0.9044</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7853</v>
+        <v>-0.6506</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7853</v>
+        <v>-1.1157</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7853</v>
+        <v>-1.1157</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7853</v>
+        <v>-1.1157</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7853</v>
+        <v>-1.1157</v>
       </c>
       <c r="N66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Xant3r</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8286</v>
+        <v>-0.6873</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2864</v>
+        <v>-0.2376</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.0014</v>
+        <v>-0.9208</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8286</v>
+        <v>-0.6873</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8286</v>
+        <v>-0.5123</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8286</v>
+        <v>-0.5123</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8286</v>
+        <v>-0.5123</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8286</v>
+        <v>-0.5123</v>
       </c>
       <c r="N67" t="n">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8364</v>
+        <v>-0.8923</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2891</v>
+        <v>-0.3084</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0049</v>
+        <v>-1.0124</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8364</v>
+        <v>-0.8923</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8364</v>
+        <v>-0.7307</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>-0.0365</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8364</v>
+        <v>-0.7307</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.858</v>
+        <v>-0.7307</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>-0.0365</v>
       </c>
       <c r="K68" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.858</v>
+        <v>-0.7672</v>
       </c>
       <c r="N68" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>zdr</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9185</v>
+        <v>-0.9218</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3175</v>
+        <v>-0.3186</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0423</v>
+        <v>-1.0256</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9185</v>
+        <v>-0.9218</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9185</v>
+        <v>-0.8158</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9185</v>
+        <v>-0.8158</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9185</v>
+        <v>-0.8368</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9185</v>
+        <v>-0.8368</v>
       </c>
       <c r="N69" t="n">
-        <v>63</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0563</v>
+        <v>-1.0971</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3651</v>
+        <v>-0.3792</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1051</v>
+        <v>-1.1039</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0563</v>
+        <v>-1.0971</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0563</v>
+        <v>-0.8286</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0563</v>
+        <v>-0.8286</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.0563</v>
+        <v>-0.8286</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0563</v>
+        <v>-0.8286</v>
       </c>
       <c r="N70" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SLIGHT</t>
+          <t>zdr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0959</v>
+        <v>-1.1337</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3788</v>
+        <v>-0.3919</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1231</v>
+        <v>-1.1202</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0959</v>
+        <v>-1.1337</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.0959</v>
+        <v>-0.9179</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.0959</v>
+        <v>-0.9179</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.0959</v>
+        <v>-0.9179</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.0959</v>
+        <v>-0.9179</v>
       </c>
       <c r="N71" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1157</v>
+        <v>-1.1699</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3857</v>
+        <v>-0.4044</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1321</v>
+        <v>-1.1364</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1157</v>
+        <v>-1.1699</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.1157</v>
+        <v>-1.0563</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.1157</v>
+        <v>-1.0563</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.1157</v>
+        <v>-1.0563</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.1157</v>
+        <v>-1.0563</v>
       </c>
       <c r="N72" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2048</v>
+        <v>-1.4177</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4165</v>
+        <v>-0.49</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1727</v>
+        <v>-1.2471</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2048</v>
+        <v>-1.4177</v>
       </c>
       <c r="F73" t="n">
         <v>-1.2048</v>
@@ -3804,139 +3804,139 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>18yM</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.217</v>
+        <v>-1.6345</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4207</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1782</v>
+        <v>-1.3439</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.217</v>
+        <v>-1.6345</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.217</v>
+        <v>-1.6201</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.217</v>
+        <v>-1.6201</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.217</v>
+        <v>-1.6201</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.217</v>
+        <v>-1.6201</v>
       </c>
       <c r="N74" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>horvy</t>
+          <t>18yM</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2372</v>
+        <v>-1.6536</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4277</v>
+        <v>-0.5716</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1874</v>
+        <v>-1.3524</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2372</v>
+        <v>-1.6536</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2372</v>
+        <v>-1.217</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2372</v>
+        <v>-1.217</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2372</v>
+        <v>-1.217</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.2372</v>
+        <v>-1.217</v>
       </c>
       <c r="N75" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>horvy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3543</v>
+        <v>-1.7176</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4681</v>
+        <v>-0.5937</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2407</v>
+        <v>-1.381</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3543</v>
+        <v>-1.7176</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3543</v>
+        <v>-1.2372</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3543</v>
+        <v>-1.2372</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3543</v>
+        <v>-1.2372</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3543</v>
+        <v>-1.2372</v>
       </c>
       <c r="N76" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77">
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5939</v>
+        <v>-1.8563</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.551</v>
+        <v>-0.6417</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3498</v>
+        <v>-1.443</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5939</v>
+        <v>-1.8563</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5939</v>
+        <v>-1.5716</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5939</v>
+        <v>-1.5716</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.635</v>
+        <v>-1.6121</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.635</v>
+        <v>-1.6121</v>
       </c>
       <c r="N77" t="n">
         <v>192</v>
@@ -3988,47 +3988,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.6201</v>
+        <v>-1.8969</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3617</v>
+        <v>-1.4611</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.6201</v>
+        <v>-1.8969</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.6201</v>
+        <v>-1.3536</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.6201</v>
+        <v>-1.3536</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.6201</v>
+        <v>-1.3536</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.6201</v>
+        <v>-1.3536</v>
       </c>
       <c r="N78" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.9486</v>
+        <v>-2.1128</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6736</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5112</v>
+        <v>-1.5576</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.9486</v>
+        <v>-2.1128</v>
       </c>
       <c r="F79" t="n">
         <v>0.9762</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.9757</v>
+        <v>-3.2547</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.0286</v>
+        <v>-1.125</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9788</v>
+        <v>-2.0676</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.9757</v>
+        <v>-3.2547</v>
       </c>
       <c r="F80" t="n">
         <v>-2.344</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-6.985</v>
+        <v>-7.2626</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.4145</v>
+        <v>-2.5104</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.8039</v>
+        <v>-3.8579</v>
       </c>
       <c r="E81" t="n">
-        <v>-6.985</v>
+        <v>-7.2626</v>
       </c>
       <c r="F81" t="n">
         <v>-5.3495</v>
@@ -12666,13 +12666,13 @@
         <v>30</v>
       </c>
       <c r="H212" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2165</v>
+        <v>1.2285</v>
       </c>
       <c r="J212" t="n">
-        <v>36.495</v>
+        <v>36.855</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.31</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8006</v>
+        <v>0.7988</v>
       </c>
       <c r="J213" t="n">
-        <v>24.018</v>
+        <v>23.964</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1146</v>
+        <v>-0.1157</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.438</v>
+        <v>-3.471</v>
       </c>
     </row>
     <row r="215">
@@ -12786,13 +12786,13 @@
         <v>30</v>
       </c>
       <c r="H215" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.535</v>
+        <v>-0.5121</v>
       </c>
       <c r="J215" t="n">
-        <v>-16.05</v>
+        <v>-15.363</v>
       </c>
     </row>
     <row r="216">
@@ -12826,13 +12826,13 @@
         <v>30</v>
       </c>
       <c r="H216" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6957</v>
+        <v>-0.6745</v>
       </c>
       <c r="J216" t="n">
-        <v>-20.871</v>
+        <v>-20.235</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.12</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2901</v>
+        <v>0.2905</v>
       </c>
       <c r="J217" t="n">
-        <v>8.702999999999999</v>
+        <v>8.715</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0997</v>
       </c>
       <c r="J218" t="n">
-        <v>2.985</v>
+        <v>2.991</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0997</v>
       </c>
       <c r="J219" t="n">
-        <v>2.985</v>
+        <v>2.991</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0254</v>
+        <v>-0.0253</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.762</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="221">
@@ -13026,13 +13026,13 @@
         <v>30</v>
       </c>
       <c r="H221" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2018</v>
+        <v>-0.2121</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.054</v>
+        <v>-6.363</v>
       </c>
     </row>
     <row r="222">
@@ -15638,7 +15638,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -16198,7 +16198,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21198,7 +21198,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -21466,19 +21466,19 @@
         <v>19</v>
       </c>
       <c r="H432" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I432" t="n">
-        <v>1.5345</v>
+        <v>1.543</v>
       </c>
       <c r="J432" t="n">
-        <v>29.1555</v>
+        <v>29.317</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -21506,13 +21506,13 @@
         <v>19</v>
       </c>
       <c r="H433" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="I433" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.7617</v>
       </c>
       <c r="J433" t="n">
-        <v>13.3779</v>
+        <v>14.4723</v>
       </c>
     </row>
     <row r="434">
@@ -21546,13 +21546,13 @@
         <v>19</v>
       </c>
       <c r="H434" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I434" t="n">
-        <v>0.624</v>
+        <v>0.643</v>
       </c>
       <c r="J434" t="n">
-        <v>11.856</v>
+        <v>12.217</v>
       </c>
     </row>
     <row r="435">
@@ -21586,13 +21586,13 @@
         <v>19</v>
       </c>
       <c r="H435" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I435" t="n">
-        <v>0.2196</v>
+        <v>0.2726</v>
       </c>
       <c r="J435" t="n">
-        <v>4.1724</v>
+        <v>5.1794</v>
       </c>
     </row>
     <row r="436">
@@ -21629,10 +21629,10 @@
         <v>0.84</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.5404</v>
+        <v>-0.5427</v>
       </c>
       <c r="J436" t="n">
-        <v>-10.2676</v>
+        <v>-10.3113</v>
       </c>
     </row>
     <row r="437">
@@ -21666,13 +21666,13 @@
         <v>19</v>
       </c>
       <c r="H437" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I437" t="n">
-        <v>0.5621</v>
+        <v>0.5473</v>
       </c>
       <c r="J437" t="n">
-        <v>10.6799</v>
+        <v>10.3987</v>
       </c>
     </row>
     <row r="438">
@@ -21706,13 +21706,13 @@
         <v>19</v>
       </c>
       <c r="H438" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I438" t="n">
-        <v>0.2997</v>
+        <v>0.281</v>
       </c>
       <c r="J438" t="n">
-        <v>5.6943</v>
+        <v>5.339</v>
       </c>
     </row>
     <row r="439">
@@ -21746,13 +21746,13 @@
         <v>19</v>
       </c>
       <c r="H439" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="I439" t="n">
-        <v>-0.3115</v>
+        <v>-0.3201</v>
       </c>
       <c r="J439" t="n">
-        <v>-5.9185</v>
+        <v>-6.0819</v>
       </c>
     </row>
     <row r="440">
@@ -21789,10 +21789,10 @@
         <v>0.58</v>
       </c>
       <c r="I440" t="n">
-        <v>-0.4381</v>
+        <v>-0.4374</v>
       </c>
       <c r="J440" t="n">
-        <v>-8.3239</v>
+        <v>-8.310600000000001</v>
       </c>
     </row>
     <row r="441">
@@ -21829,10 +21829,10 @@
         <v>0.47</v>
       </c>
       <c r="I441" t="n">
-        <v>-0.5336</v>
+        <v>-0.533</v>
       </c>
       <c r="J441" t="n">
-        <v>-10.1384</v>
+        <v>-10.127</v>
       </c>
     </row>
     <row r="442">
@@ -26198,7 +26198,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
